--- a/output/pdf_financials_xlsx/ECU.xlsx
+++ b/output/pdf_financials_xlsx/ECU.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.905719</v>
+        <v>-2.905719</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5.241937</v>
+        <v>-5.241937</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.918948</v>
+        <v>-1.918948</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7.149505</v>
+        <v>-7.149505</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.567643</v>
+        <v>-2.567643</v>
       </c>
     </row>
     <row r="17">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.905719</v>
+        <v>-2.905719</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.241937</v>
+        <v>-5.241937</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.918948</v>
+        <v>-1.918948</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7.149505</v>
+        <v>-7.149505</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.567643</v>
+        <v>-2.567643</v>
       </c>
     </row>
     <row r="21">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.905719</v>
+        <v>-2.905719</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.241937</v>
+        <v>-5.241937</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.918948</v>
+        <v>-1.918948</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7.149505</v>
+        <v>-7.149505</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.567643</v>
+        <v>-2.567643</v>
       </c>
     </row>
     <row r="24">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.905719</v>
+        <v>-2.905719</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.241937</v>
+        <v>-5.241937</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.918948</v>
+        <v>-1.918948</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7.149505</v>
+        <v>-7.149505</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.567643</v>
+        <v>-2.567643</v>
       </c>
     </row>
     <row r="28">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.910859</v>
+        <v>-2.900579</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.259699</v>
+        <v>-5.224175</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.958614</v>
+        <v>-1.879282</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7.208447</v>
+        <v>-7.090563</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.622346</v>
+        <v>-2.51294</v>
       </c>
     </row>
     <row r="30">
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2504,19 +2504,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.416811</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.008624</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.274351</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.59133</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.514946</v>
       </c>
     </row>
     <row r="93">
@@ -4106,7 +4106,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4297,7 +4301,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4635,7 +4643,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>1.416811</v>
       </c>
@@ -7133,19 +7145,19 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2.905719</v>
+        <v>-2.905719</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>5.241937</v>
+        <v>-5.241937</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1.918948</v>
+        <v>-1.918948</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>7.149505</v>
+        <v>-7.149505</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>2.567643</v>
+        <v>-2.567643</v>
       </c>
     </row>
     <row r="95">

--- a/output/pdf_financials_xlsx/ECU.xlsx
+++ b/output/pdf_financials_xlsx/ECU.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017817</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.027702</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021569</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011471</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.092626</v>
       </c>
     </row>
     <row r="13">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.905719</v>
+        <v>-2.887902</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.241937</v>
+        <v>-5.214235</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.918948</v>
+        <v>-1.897379</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.149505</v>
+        <v>-7.138034</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.567643</v>
+        <v>-2.475017</v>
       </c>
     </row>
     <row r="28">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.900579</v>
+        <v>-2.882762</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.224175</v>
+        <v>-5.196473</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.879282</v>
+        <v>-1.857713</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.090563</v>
+        <v>-7.079092</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.51294</v>
+        <v>-2.420314</v>
       </c>
     </row>
     <row r="30">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.832949</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.079849</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.228429</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.832949</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.079849</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.228429</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.766931</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.272131</v>
+        <v>0.192282</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.215791</v>
@@ -3199,13 +3199,13 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019105</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024807</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.034484</v>
       </c>
     </row>
     <row r="125">
@@ -3221,13 +3221,13 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019105</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024807</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.034484</v>
       </c>
     </row>
     <row r="126">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -5364,7 +5364,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -7028,7 +7032,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">

--- a/output/pdf_financials_xlsx/ECU.xlsx
+++ b/output/pdf_financials_xlsx/ECU.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.829836</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.834962</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.79545</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.462367</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.461514</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.655412</v>
+        <v>1.485248</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.8121119999999999</v>
+        <v>1.647074</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.529973</v>
+        <v>1.325423</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.510868</v>
+        <v>0.973235</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7590209999999999</v>
+        <v>1.220535</v>
       </c>
     </row>
     <row r="11">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.023942</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -5608,7 +5608,11 @@
           <t>Loss on disposal of property and equipment 5</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -6738,7 +6742,11 @@
           <t>Personnel costs 10</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>0.829836</v>
       </c>
@@ -8029,7 +8037,11 @@
           <t>Personnel costs 11</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ECU.xlsx
+++ b/output/pdf_financials_xlsx/ECU.xlsx
@@ -2844,13 +2844,13 @@
         <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0</v>
+        <v>1.541503</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>5.134671</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.08053399999999999</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.028093</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024211</v>
       </c>
     </row>
     <row r="112">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.08053399999999999</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.028093</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024211</v>
       </c>
     </row>
     <row r="135">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.011191</v>
+        <v>-2.091725</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.227486</v>
+        <v>-2.255579</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.858163</v>
@@ -3457,7 +3457,7 @@
         <v>-1.314159</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.350897</v>
+        <v>-1.375108</v>
       </c>
     </row>
   </sheetData>
@@ -4910,7 +4910,11 @@
           <t>Impairment charge 6</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -5132,7 +5136,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5247,7 +5255,11 @@
           <t>Proceeds from issuance of common shares – private placement 8</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>6.8988</v>
       </c>
@@ -5860,7 +5872,11 @@
           <t>Proceeds from issuance of common shares – private placement 9</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -6186,7 +6202,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>-0.08053399999999999</v>
       </c>
